--- a/data/nzd0135/nzd0135.xlsx
+++ b/data/nzd0135/nzd0135.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I655"/>
+  <dimension ref="A1:I660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22031,6 +22031,171 @@
         <v>387.16</v>
       </c>
       <c r="I655" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>360.78</v>
+      </c>
+      <c r="C656" t="n">
+        <v>372.92</v>
+      </c>
+      <c r="D656" t="n">
+        <v>370.85</v>
+      </c>
+      <c r="E656" t="n">
+        <v>378.73</v>
+      </c>
+      <c r="F656" t="n">
+        <v>378.08</v>
+      </c>
+      <c r="G656" t="n">
+        <v>379.89</v>
+      </c>
+      <c r="H656" t="n">
+        <v>387.37</v>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>360.08</v>
+      </c>
+      <c r="C657" t="n">
+        <v>372.33</v>
+      </c>
+      <c r="D657" t="n">
+        <v>370.73</v>
+      </c>
+      <c r="E657" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="F657" t="n">
+        <v>378.46</v>
+      </c>
+      <c r="G657" t="n">
+        <v>379.93</v>
+      </c>
+      <c r="H657" t="n">
+        <v>387.86</v>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>359.14</v>
+      </c>
+      <c r="C658" t="n">
+        <v>372.68</v>
+      </c>
+      <c r="D658" t="n">
+        <v>371.56</v>
+      </c>
+      <c r="E658" t="n">
+        <v>378.85</v>
+      </c>
+      <c r="F658" t="n">
+        <v>379.23</v>
+      </c>
+      <c r="G658" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="H658" t="n">
+        <v>388.25</v>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>356.64</v>
+      </c>
+      <c r="C659" t="n">
+        <v>371.38</v>
+      </c>
+      <c r="D659" t="n">
+        <v>371.06</v>
+      </c>
+      <c r="E659" t="n">
+        <v>378.58</v>
+      </c>
+      <c r="F659" t="n">
+        <v>379.68</v>
+      </c>
+      <c r="G659" t="n">
+        <v>379.96</v>
+      </c>
+      <c r="H659" t="n">
+        <v>387.86</v>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>356.64</v>
+      </c>
+      <c r="C660" t="n">
+        <v>371.59</v>
+      </c>
+      <c r="D660" t="n">
+        <v>371.08</v>
+      </c>
+      <c r="E660" t="n">
+        <v>378.8</v>
+      </c>
+      <c r="F660" t="n">
+        <v>379.66</v>
+      </c>
+      <c r="G660" t="n">
+        <v>380.04</v>
+      </c>
+      <c r="H660" t="n">
+        <v>387.95</v>
+      </c>
+      <c r="I660" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22047,7 +22212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B681"/>
+  <dimension ref="A1:B686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28860,6 +29025,56 @@
       </c>
       <c r="B681" t="n">
         <v>-0.86</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -29028,28 +29243,28 @@
         <v>0.1028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03023677509219024</v>
+        <v>0.01670370571907886</v>
       </c>
       <c r="J2" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="K2" t="n">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001604070390815782</v>
+        <v>0.0004891357805592023</v>
       </c>
       <c r="M2" t="n">
-        <v>4.607879718379364</v>
+        <v>4.638988992023456</v>
       </c>
       <c r="N2" t="n">
-        <v>31.95425785670143</v>
+        <v>32.32775542956892</v>
       </c>
       <c r="O2" t="n">
-        <v>5.652809731160374</v>
+        <v>5.685750208158016</v>
       </c>
       <c r="P2" t="n">
-        <v>366.7898509334265</v>
+        <v>366.9343651946303</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29106,28 +29321,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05405523878778751</v>
+        <v>-0.05767724977323368</v>
       </c>
       <c r="J3" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="K3" t="n">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01598221725599014</v>
+        <v>0.01838559492589997</v>
       </c>
       <c r="M3" t="n">
-        <v>2.525001442740197</v>
+        <v>2.525316418025365</v>
       </c>
       <c r="N3" t="n">
-        <v>10.10229192559951</v>
+        <v>10.07080364511255</v>
       </c>
       <c r="O3" t="n">
-        <v>3.178410282767081</v>
+        <v>3.173452953032792</v>
       </c>
       <c r="P3" t="n">
-        <v>376.0330703617918</v>
+        <v>376.0717486763069</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29184,28 +29399,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0148677167972793</v>
+        <v>-0.01363911954021695</v>
       </c>
       <c r="J4" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="K4" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0009471411849558686</v>
+        <v>0.0008107409375824881</v>
       </c>
       <c r="M4" t="n">
-        <v>2.774539194808686</v>
+        <v>2.759222427315764</v>
       </c>
       <c r="N4" t="n">
-        <v>13.15985199248682</v>
+        <v>13.06554402301604</v>
       </c>
       <c r="O4" t="n">
-        <v>3.627651029590197</v>
+        <v>3.614629168118916</v>
       </c>
       <c r="P4" t="n">
-        <v>370.641585483087</v>
+        <v>370.6285138153606</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29262,28 +29477,28 @@
         <v>0.0602</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05351668955113336</v>
+        <v>-0.05084323166171207</v>
       </c>
       <c r="J5" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="K5" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01401756807880028</v>
+        <v>0.01286099520740513</v>
       </c>
       <c r="M5" t="n">
-        <v>2.489229505820269</v>
+        <v>2.484628207392509</v>
       </c>
       <c r="N5" t="n">
-        <v>11.37008428877115</v>
+        <v>11.30730748453589</v>
       </c>
       <c r="O5" t="n">
-        <v>3.371955558540348</v>
+        <v>3.362634009899961</v>
       </c>
       <c r="P5" t="n">
-        <v>378.3588141770585</v>
+        <v>378.3303723461456</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29340,28 +29555,28 @@
         <v>0.0751</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07968596358966039</v>
+        <v>-0.0768605040167027</v>
       </c>
       <c r="J6" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="K6" t="n">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03828769003908594</v>
+        <v>0.03620317972785458</v>
       </c>
       <c r="M6" t="n">
-        <v>2.26980033411962</v>
+        <v>2.267866538514748</v>
       </c>
       <c r="N6" t="n">
-        <v>8.967882039040081</v>
+        <v>8.928726417663881</v>
       </c>
       <c r="O6" t="n">
-        <v>2.994642222209538</v>
+        <v>2.988097457859078</v>
       </c>
       <c r="P6" t="n">
-        <v>379.3018912221435</v>
+        <v>379.2717264740076</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29418,28 +29633,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01976968509575223</v>
+        <v>-0.01697527372387779</v>
       </c>
       <c r="J7" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="K7" t="n">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001783869322059206</v>
+        <v>0.001336010452918868</v>
       </c>
       <c r="M7" t="n">
-        <v>2.805712503211597</v>
+        <v>2.800143194638034</v>
       </c>
       <c r="N7" t="n">
-        <v>12.2970593796223</v>
+        <v>12.22889998452034</v>
       </c>
       <c r="O7" t="n">
-        <v>3.506716324372745</v>
+        <v>3.496984412965026</v>
       </c>
       <c r="P7" t="n">
-        <v>378.6742052455782</v>
+        <v>378.6443796162609</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29496,28 +29711,28 @@
         <v>0.1107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008606343474684846</v>
+        <v>0.0125271622269984</v>
       </c>
       <c r="J8" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="K8" t="n">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003414442142336549</v>
+        <v>0.0007326680092379911</v>
       </c>
       <c r="M8" t="n">
-        <v>2.766222328912244</v>
+        <v>2.765616472962572</v>
       </c>
       <c r="N8" t="n">
-        <v>12.23304322542828</v>
+        <v>12.19021224020963</v>
       </c>
       <c r="O8" t="n">
-        <v>3.497576764765611</v>
+        <v>3.491448444443885</v>
       </c>
       <c r="P8" t="n">
-        <v>385.0315653440128</v>
+        <v>384.989715376734</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29555,7 +29770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I655"/>
+  <dimension ref="A1:I660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60295,6 +60510,241 @@
         </is>
       </c>
     </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>-36.55618720985364,174.70741448506666</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>-36.556891092920054,174.70734452118822</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>-36.55759287531453,174.70737554321258</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>-36.55828976846578,174.70757658653875</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>-36.55899014271611,174.70773993080493</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>-36.559684877896736,174.7079684694978</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>-36.56036821200002,174.70825267114506</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>-36.55618583795419,174.70740685239258</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>-36.556890708910124,174.70733794735776</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>-36.557592990855255,174.70737421032203</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>-36.55829012480768,174.70757405535463</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>-36.55898937539769,174.70774406807263</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>-36.559684790930085,174.70796890316618</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>-36.56036716106302,174.70825798803526</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>-36.55618399568842,174.70739660280202</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>-36.556890936712676,174.7073418470877</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>-36.55759219169826,174.7073834294816</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>-36.55828958254824,174.70757790715652</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>-36.558987820567836,174.7077524514832</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>-36.559684377838394,174.7079709630908</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>-36.56036632460278,174.70826221984575</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>-36.556179096041106,174.70736934325484</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>-36.55689009058828,174.70732736237665</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>-36.55759267311822,174.70737787577104</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>-36.55829000086267,174.7075749357665</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>-36.55898691190076,174.70775735087884</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>-36.55968472570508,174.70796922841743</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>-36.56036716106302,174.70825798803526</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>-36.556179096041106,174.70736934325484</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>-36.55689022727004,174.70732970221457</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>-36.55759265386143,174.70737809791947</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>-36.558289660013884,174.70757735689912</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>-36.55898695228596,174.70775713312793</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>-36.55968455177174,174.7079700957541</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>-36.56036696803375,174.70825896460693</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0135/nzd0135.xlsx
+++ b/data/nzd0135/nzd0135.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I660"/>
+  <dimension ref="A1:I663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22175,7 +22175,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>356.64</v>
+        <v>356.63</v>
       </c>
       <c r="C660" t="n">
         <v>371.59</v>
@@ -22196,6 +22196,105 @@
         <v>387.95</v>
       </c>
       <c r="I660" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="C661" t="n">
+        <v>372.23</v>
+      </c>
+      <c r="D661" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="E661" t="n">
+        <v>379.4</v>
+      </c>
+      <c r="F661" t="n">
+        <v>379.88</v>
+      </c>
+      <c r="G661" t="n">
+        <v>380.43</v>
+      </c>
+      <c r="H661" t="n">
+        <v>388.22</v>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>356.02</v>
+      </c>
+      <c r="C662" t="n">
+        <v>373</v>
+      </c>
+      <c r="D662" t="n">
+        <v>372.11</v>
+      </c>
+      <c r="E662" t="n">
+        <v>380.46</v>
+      </c>
+      <c r="F662" t="n">
+        <v>380.42</v>
+      </c>
+      <c r="G662" t="n">
+        <v>381.24</v>
+      </c>
+      <c r="H662" t="n">
+        <v>388.57</v>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>354.68</v>
+      </c>
+      <c r="C663" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="D663" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="E663" t="n">
+        <v>380.36</v>
+      </c>
+      <c r="F663" t="n">
+        <v>380.64</v>
+      </c>
+      <c r="G663" t="n">
+        <v>381.26</v>
+      </c>
+      <c r="H663" t="n">
+        <v>388.65</v>
+      </c>
+      <c r="I663" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22212,7 +22311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B686"/>
+  <dimension ref="A1:B689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29075,6 +29174,36 @@
       </c>
       <c r="B686" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -29243,28 +29372,28 @@
         <v>0.1028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01670370571907886</v>
+        <v>0.006278514176904331</v>
       </c>
       <c r="J2" t="n">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="K2" t="n">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004891357805592023</v>
+        <v>6.857163636930785e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>4.638988992023456</v>
+        <v>4.668951808727975</v>
       </c>
       <c r="N2" t="n">
-        <v>32.32775542956892</v>
+        <v>32.78202372607597</v>
       </c>
       <c r="O2" t="n">
-        <v>5.685750208158016</v>
+        <v>5.725558813432621</v>
       </c>
       <c r="P2" t="n">
-        <v>366.9343651946303</v>
+        <v>367.0461541441348</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29321,28 +29450,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05767724977323368</v>
+        <v>-0.05934744114070069</v>
       </c>
       <c r="J3" t="n">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="K3" t="n">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01838559492589997</v>
+        <v>0.0196121379524854</v>
       </c>
       <c r="M3" t="n">
-        <v>2.525316418025365</v>
+        <v>2.523000008846264</v>
       </c>
       <c r="N3" t="n">
-        <v>10.07080364511255</v>
+        <v>10.04091474604198</v>
       </c>
       <c r="O3" t="n">
-        <v>3.173452953032792</v>
+        <v>3.168740245908771</v>
       </c>
       <c r="P3" t="n">
-        <v>376.0717486763069</v>
+        <v>376.0896540234339</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29399,28 +29528,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01363911954021695</v>
+        <v>-0.01183377489174351</v>
       </c>
       <c r="J4" t="n">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="K4" t="n">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008107409375824881</v>
+        <v>0.0006157663091385102</v>
       </c>
       <c r="M4" t="n">
-        <v>2.759222427315764</v>
+        <v>2.755029547514232</v>
       </c>
       <c r="N4" t="n">
-        <v>13.06554402301604</v>
+        <v>13.02714357395804</v>
       </c>
       <c r="O4" t="n">
-        <v>3.614629168118916</v>
+        <v>3.609313449114393</v>
       </c>
       <c r="P4" t="n">
-        <v>370.6285138153606</v>
+        <v>370.6092183520656</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29477,28 +29606,28 @@
         <v>0.0602</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05084323166171207</v>
+        <v>-0.04804052595326921</v>
       </c>
       <c r="J5" t="n">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="K5" t="n">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01286099520740513</v>
+        <v>0.01157032791184509</v>
       </c>
       <c r="M5" t="n">
-        <v>2.484628207392509</v>
+        <v>2.488187293333943</v>
       </c>
       <c r="N5" t="n">
-        <v>11.30730748453589</v>
+        <v>11.30060345930655</v>
       </c>
       <c r="O5" t="n">
-        <v>3.362634009899961</v>
+        <v>3.361637020754405</v>
       </c>
       <c r="P5" t="n">
-        <v>378.3303723461456</v>
+        <v>378.3004251114187</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29555,28 +29684,28 @@
         <v>0.0751</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0768605040167027</v>
+        <v>-0.07404710475792586</v>
       </c>
       <c r="J6" t="n">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="K6" t="n">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03620317972785458</v>
+        <v>0.03386406583300439</v>
       </c>
       <c r="M6" t="n">
-        <v>2.267866538514748</v>
+        <v>2.272896094962118</v>
       </c>
       <c r="N6" t="n">
-        <v>8.928726417663881</v>
+        <v>8.932201828154104</v>
       </c>
       <c r="O6" t="n">
-        <v>2.988097457859078</v>
+        <v>2.988678943639498</v>
       </c>
       <c r="P6" t="n">
-        <v>379.2717264740076</v>
+        <v>379.2415679627667</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29633,28 +29762,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01697527372387779</v>
+        <v>-0.01445519998653365</v>
       </c>
       <c r="J7" t="n">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="K7" t="n">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001336010452918868</v>
+        <v>0.0009763114337735246</v>
       </c>
       <c r="M7" t="n">
-        <v>2.800143194638034</v>
+        <v>2.801518356486745</v>
       </c>
       <c r="N7" t="n">
-        <v>12.22889998452034</v>
+        <v>12.20896495544974</v>
       </c>
       <c r="O7" t="n">
-        <v>3.496984412965026</v>
+        <v>3.494132933282554</v>
       </c>
       <c r="P7" t="n">
-        <v>378.6443796162609</v>
+        <v>378.617364604609</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29711,28 +29840,28 @@
         <v>0.1107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0125271622269984</v>
+        <v>0.01537116001431778</v>
       </c>
       <c r="J8" t="n">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="K8" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0007326680092379911</v>
+        <v>0.001109972463666842</v>
       </c>
       <c r="M8" t="n">
-        <v>2.765616472962572</v>
+        <v>2.768261841094545</v>
       </c>
       <c r="N8" t="n">
-        <v>12.19021224020963</v>
+        <v>12.17942032622988</v>
       </c>
       <c r="O8" t="n">
-        <v>3.491448444443885</v>
+        <v>3.489902624175907</v>
       </c>
       <c r="P8" t="n">
-        <v>384.989715376734</v>
+        <v>384.9592286557404</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29770,7 +29899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I660"/>
+  <dimension ref="A1:I663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60706,7 +60835,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>-36.556179096041106,174.70736934325484</t>
+          <t>-36.55617907644252,174.70736923421669</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -60740,6 +60869,147 @@
         </is>
       </c>
       <c r="I660" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>-36.55617940961873,174.7073710878658</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>-36.55689064382366,174.7073368331492</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>-36.557592345752674,174.70738165229423</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>-36.55828873042599,174.70758395998794</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>-36.558986508048655,174.70775952838795</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>-36.55968370384663,174.7079743240204</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>-36.56036638894589,174.70826189432188</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>-36.556177880927585,174.70736258288767</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>-36.556891144989166,174.70734541255507</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>-36.55759166213602,174.7073895385631</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>-36.5582870881532,174.70759562544447</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>-36.5589854176478,174.7077654076625</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>-36.559681942770915,174.70798310580395</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>-36.56036563827634,174.7082656921004</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>-36.55617525471319,174.70734797177215</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>-36.55689097576453,174.70734251561282</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>-36.5575905163548,174.7074027563937</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>-36.55828724308465,174.70759452492973</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>-36.55898497341034,174.70776780292243</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>-36.55968189928755,174.70798332263809</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>-36.56036546669471,174.70826656016405</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0135/nzd0135.xlsx
+++ b/data/nzd0135/nzd0135.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I663"/>
+  <dimension ref="A1:I664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22295,6 +22295,39 @@
         <v>388.65</v>
       </c>
       <c r="I663" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>355.36</v>
+      </c>
+      <c r="C664" t="n">
+        <v>373.35</v>
+      </c>
+      <c r="D664" t="n">
+        <v>374.2</v>
+      </c>
+      <c r="E664" t="n">
+        <v>381.19</v>
+      </c>
+      <c r="F664" t="n">
+        <v>381.09</v>
+      </c>
+      <c r="G664" t="n">
+        <v>381.81</v>
+      </c>
+      <c r="H664" t="n">
+        <v>389.12</v>
+      </c>
+      <c r="I664" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22311,7 +22344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B689"/>
+  <dimension ref="A1:B690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29204,6 +29237,16 @@
       </c>
       <c r="B689" t="n">
         <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -29372,28 +29415,28 @@
         <v>0.1028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006278514176904331</v>
+        <v>0.002708467029032132</v>
       </c>
       <c r="J2" t="n">
+        <v>663</v>
+      </c>
+      <c r="K2" t="n">
         <v>662</v>
       </c>
-      <c r="K2" t="n">
-        <v>661</v>
-      </c>
       <c r="L2" t="n">
-        <v>6.857163636930785e-05</v>
+        <v>1.272329488022361e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>4.668951808727975</v>
+        <v>4.679523399436654</v>
       </c>
       <c r="N2" t="n">
-        <v>32.78202372607597</v>
+        <v>32.94391485055139</v>
       </c>
       <c r="O2" t="n">
-        <v>5.725558813432621</v>
+        <v>5.739678984973932</v>
       </c>
       <c r="P2" t="n">
-        <v>367.0461541441348</v>
+        <v>367.0845490369629</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29450,28 +29493,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05934744114070069</v>
+        <v>-0.05968679930087881</v>
       </c>
       <c r="J3" t="n">
+        <v>663</v>
+      </c>
+      <c r="K3" t="n">
         <v>662</v>
       </c>
-      <c r="K3" t="n">
-        <v>661</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0196121379524854</v>
+        <v>0.01989585175116804</v>
       </c>
       <c r="M3" t="n">
-        <v>2.523000008846264</v>
+        <v>2.521038371675595</v>
       </c>
       <c r="N3" t="n">
-        <v>10.04091474604198</v>
+        <v>10.02765747594565</v>
       </c>
       <c r="O3" t="n">
-        <v>3.168740245908771</v>
+        <v>3.166647671583571</v>
       </c>
       <c r="P3" t="n">
-        <v>376.0896540234339</v>
+        <v>376.0933037287881</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29528,28 +29571,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01183377489174351</v>
+        <v>-0.0106624809221013</v>
       </c>
       <c r="J4" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="K4" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006157663091385102</v>
+        <v>0.0005007960870501149</v>
       </c>
       <c r="M4" t="n">
-        <v>2.755029547514232</v>
+        <v>2.756251261086131</v>
       </c>
       <c r="N4" t="n">
-        <v>13.02714357395804</v>
+        <v>13.03042102091966</v>
       </c>
       <c r="O4" t="n">
-        <v>3.609313449114393</v>
+        <v>3.609767446930572</v>
       </c>
       <c r="P4" t="n">
-        <v>370.6092183520656</v>
+        <v>370.5966666258179</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29606,28 +29649,28 @@
         <v>0.0602</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04804052595326921</v>
+        <v>-0.04678233451640108</v>
       </c>
       <c r="J5" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="K5" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01157032791184509</v>
+        <v>0.01099060205264102</v>
       </c>
       <c r="M5" t="n">
-        <v>2.488187293333943</v>
+        <v>2.491082152084974</v>
       </c>
       <c r="N5" t="n">
-        <v>11.30060345930655</v>
+        <v>11.31001298782198</v>
       </c>
       <c r="O5" t="n">
-        <v>3.361637020754405</v>
+        <v>3.363036275127282</v>
       </c>
       <c r="P5" t="n">
-        <v>378.3004251114187</v>
+        <v>378.2869421815207</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29684,28 +29727,28 @@
         <v>0.0751</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07404710475792586</v>
+        <v>-0.07288441372232876</v>
       </c>
       <c r="J6" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="K6" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03386406583300439</v>
+        <v>0.0328728725257712</v>
       </c>
       <c r="M6" t="n">
-        <v>2.272896094962118</v>
+        <v>2.275813712758586</v>
       </c>
       <c r="N6" t="n">
-        <v>8.932201828154104</v>
+        <v>8.941153368915986</v>
       </c>
       <c r="O6" t="n">
-        <v>2.988678943639498</v>
+        <v>2.990176143459777</v>
       </c>
       <c r="P6" t="n">
-        <v>379.2415679627667</v>
+        <v>379.2290678036409</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29762,28 +29805,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01445519998653365</v>
+        <v>-0.01337566434134739</v>
       </c>
       <c r="J7" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="K7" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009763114337735246</v>
+        <v>0.000837595626936638</v>
       </c>
       <c r="M7" t="n">
-        <v>2.801518356486745</v>
+        <v>2.803279373305301</v>
       </c>
       <c r="N7" t="n">
-        <v>12.20896495544974</v>
+        <v>12.20986078238991</v>
       </c>
       <c r="O7" t="n">
-        <v>3.494132933282554</v>
+        <v>3.494261121094116</v>
       </c>
       <c r="P7" t="n">
-        <v>378.617364604609</v>
+        <v>378.6057584539345</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29840,28 +29883,28 @@
         <v>0.1107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01537116001431778</v>
+        <v>0.01649711997150736</v>
       </c>
       <c r="J8" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="K8" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001109972463666842</v>
+        <v>0.001280484640466373</v>
       </c>
       <c r="M8" t="n">
-        <v>2.768261841094545</v>
+        <v>2.770096369283279</v>
       </c>
       <c r="N8" t="n">
-        <v>12.17942032622988</v>
+        <v>12.18206505014074</v>
       </c>
       <c r="O8" t="n">
-        <v>3.489902624175907</v>
+        <v>3.490281514454205</v>
       </c>
       <c r="P8" t="n">
-        <v>384.9592286557404</v>
+        <v>384.9471223960055</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29899,7 +29942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I663"/>
+  <dimension ref="A1:I664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61015,6 +61058,53 @@
         </is>
       </c>
     </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>-36.55617658741923,174.70735538636796</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>-36.55689137279146,174.70734931228503</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>-36.55758964979663,174.70741275307202</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>-36.55828595715336,174.70760365920196</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>-36.558984064742646,174.7077727023177</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>-36.55968070349504,174.7079892855773</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>-36.5603644586525,174.70827166003798</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
